--- a/Top_15_Triple_S_Watchlist.xlsx
+++ b/Top_15_Triple_S_Watchlist.xlsx
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-20 09:08</t>
+          <t>2026-09-20 09:22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -537,7 +537,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07</t>
+          <t>2026-09-20 09:22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -581,7 +581,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-20 09:08</t>
+          <t>2026-09-20 09:22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -625,7 +625,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07</t>
+          <t>2026-09-20 09:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -669,7 +669,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-20 09:05</t>
+          <t>2026-09-20 09:20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-20 09:05</t>
+          <t>2026-09-20 09:20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -757,7 +757,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-20 09:05</t>
+          <t>2026-09-20 09:20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07</t>
+          <t>2026-09-20 09:22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07</t>
+          <t>2026-09-20 09:22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -889,7 +889,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-20 09:06</t>
+          <t>2026-09-20 09:21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -933,7 +933,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-20 09:08</t>
+          <t>2026-09-20 09:23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -977,7 +977,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-20 09:06</t>
+          <t>2026-09-20 09:21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1021,7 +1021,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-20 09:06</t>
+          <t>2026-09-20 09:21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1065,7 +1065,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-20 09:05</t>
+          <t>2026-09-20 09:20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1109,7 +1109,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07</t>
+          <t>2026-09-20 09:22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">

--- a/Top_15_Triple_S_Watchlist.xlsx
+++ b/Top_15_Triple_S_Watchlist.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watchlist" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,13 +28,35 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -55,11 +77,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,337 +454,351 @@
   </sheetPr>
   <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Scan_Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Quality Score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Above SMA150</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>RVOL</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Upper Line</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Lower Line</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Stop Loss</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Take Profit</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-09-20 09:22</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:55</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>WRB</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="3" t="n">
         <v>69.98999999999999</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>NEAR_SUPPORT (LONG WATCH)</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="F2" t="b">
+      <c r="F2" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="3" t="n">
         <v>51.1</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="3" t="n">
         <v>3.13</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="3" t="n">
         <v>77.44999694824219</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="3" t="n">
         <v>67.36000061035156</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="3" t="n">
         <v>67.02</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="3" t="n">
         <v>77.45</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-09-20 09:22</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:55</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>ROKU</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="4" t="n">
         <v>153.68</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>NEAR_RESISTANCE (SHORT WATCH)</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="F3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="F3" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4" t="n">
         <v>35.5</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="4" t="n">
         <v>2.2</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="4" t="n">
         <v>159.8899993896484</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="4" t="n">
         <v>134.3600006103516</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="4" t="n">
         <v>160.69</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="4" t="n">
         <v>134.36</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-09-20 09:22</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:55</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>WBD</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="4" t="n">
         <v>27.81</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>NEAR_RESISTANCE (SHORT WATCH)</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="F4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="F4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="n">
         <v>30.8</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="4" t="n">
         <v>2.06</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="4" t="n">
         <v>28.98999977111816</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="4" t="n">
         <v>25.25</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="4" t="n">
         <v>29.13</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="4" t="n">
         <v>25.25</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-09-20 09:22</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:55</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>RSG</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="4" t="n">
         <v>218.04</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>NEAR_RESISTANCE (SHORT WATCH)</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="F5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="n">
         <v>39.5</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="4" t="n">
         <v>2.86</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="4" t="n">
         <v>228.2200012207031</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="4" t="n">
         <v>204.8000946044922</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="4" t="n">
         <v>229.36</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="4" t="n">
         <v>204.8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-09-20 09:20</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:55</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>AWK</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="4" t="n">
         <v>135.93</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>NEAR_RESISTANCE (SHORT WATCH)</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="F6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="n">
         <v>36.2</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="4" t="n">
         <v>2.09</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="4" t="n">
         <v>142.3699951171875</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="4" t="n">
         <v>128.6199951171875</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="4" t="n">
         <v>143.08</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="4" t="n">
         <v>128.62</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-09-20 09:20</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:55</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>BIIB</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="4" t="n">
         <v>215.5</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>NEAR_RESISTANCE (SHORT WATCH)</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="F7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="n">
         <v>47.6</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="4" t="n">
         <v>4.09</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="4" t="n">
         <v>225.8000030517578</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="4" t="n">
         <v>186.0249938964844</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="4" t="n">
         <v>226.93</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="4" t="n">
         <v>186.02</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-20 09:20</t>
+          <t>2026-09-20 10:55</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -799,53 +840,53 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-09-20 09:22</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:55</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="4" t="n">
         <v>367.61</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>NEAR_RESISTANCE (SHORT WATCH)</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="F9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
         <v>29.2</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="4" t="n">
         <v>3.01</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="4" t="n">
         <v>385.5698852539062</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="4" t="n">
         <v>330.0700073242188</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="4" t="n">
         <v>387.5</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="4" t="n">
         <v>330.07</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-20 09:22</t>
+          <t>2026-09-20 10:55</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -887,53 +928,53 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-09-20 09:21</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:55</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="4" t="n">
         <v>88.15000000000001</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>NEAR_RESISTANCE (SHORT WATCH)</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
+      <c r="F11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="4" t="n">
         <v>1.9</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="4" t="n">
         <v>92.48999786376953</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="4" t="n">
         <v>79.97000122070312</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="4" t="n">
         <v>92.95</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="4" t="n">
         <v>79.97</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-20 09:23</t>
+          <t>2026-09-20 10:55</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -977,7 +1018,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-20 09:21</t>
+          <t>2026-09-20 10:55</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1021,7 +1062,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-20 09:21</t>
+          <t>2026-09-20 10:55</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,90 +1104,90 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-09-20 09:20</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:55</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>AMT</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="4" t="n">
         <v>173.99</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>NEAR_RESISTANCE (SHORT WATCH)</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
+      <c r="F15" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4" t="n">
         <v>38.1</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="4" t="n">
         <v>1.19</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" s="4" t="n">
         <v>180.9799957275391</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="4" t="n">
         <v>160.0599975585938</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15" s="4" t="n">
         <v>181.88</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15" s="4" t="n">
         <v>160.06</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-09-20 09:22</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:55</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>NXPI</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="3" t="n">
         <v>228.32</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>NEAR_SUPPORT (LONG WATCH)</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="F16" t="b">
+      <c r="F16" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="3" t="n">
         <v>70.8</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" s="3" t="n">
         <v>1.75</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" s="3" t="n">
         <v>307.3800048828125</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="3" t="n">
         <v>216.6600036621094</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16" s="3" t="n">
         <v>215.58</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16" s="3" t="n">
         <v>307.38</v>
       </c>
     </row>

--- a/Top_15_Triple_S_Watchlist.xlsx
+++ b/Top_15_Triple_S_Watchlist.xlsx
@@ -532,194 +532,194 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:55</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>WRB</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>69.98999999999999</v>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-21 19:13</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>744.5599999999999</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>NEUTRAL_ZONE</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>45</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>81</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I2" t="n">
+        <v>749.489990234375</v>
+      </c>
+      <c r="J2" t="n">
+        <v>524.5189819335938</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-21 19:13</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>121.33</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NEUTRAL_ZONE</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>44</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I3" t="n">
+        <v>142.3399963378906</v>
+      </c>
+      <c r="J3" t="n">
+        <v>81.79000091552734</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-21 19:13</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>612.4</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NEUTRAL_ZONE</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>44</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="I4" t="n">
+        <v>615.989990234375</v>
+      </c>
+      <c r="J4" t="n">
+        <v>424.0315856933594</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21 19:13</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>CSCO</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>110.83</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>NEAR_SUPPORT (LONG WATCH)</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="F2" s="3" t="b">
+      <c r="E5" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="F5" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="G2" s="3" t="n">
-        <v>51.1</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>77.44999694824219</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>67.36000061035156</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>67.02</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>77.45</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:55</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>ROKU</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>153.68</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>NEAR_RESISTANCE (SHORT WATCH)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="F3" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>159.8899993896484</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>134.3600006103516</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>160.69</v>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>134.36</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:55</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>WBD</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>27.81</v>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>NEAR_RESISTANCE (SHORT WATCH)</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="F4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>28.98999977111816</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>25.25</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>29.13</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>25.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:55</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>RSG</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>218.04</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>NEAR_RESISTANCE (SHORT WATCH)</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="F5" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>228.2200012207031</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>204.8000946044922</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>229.36</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>204.8</v>
+      <c r="G5" s="3" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>124.7102966308594</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>107.3899993896484</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>124.71</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20 10:55</t>
+          <t>2026-09-21 19:14</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>AWK</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>135.93</v>
+        <v>154.34</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -727,43 +727,43 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F6" s="4" t="b">
         <v>0</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>36.2</v>
+        <v>46.5</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>2.09</v>
+        <v>0.57</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>142.3699951171875</v>
+        <v>159.8899993896484</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>128.6199951171875</v>
+        <v>134.3600006103516</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>143.08</v>
+        <v>160.69</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>128.62</v>
+        <v>134.36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20 10:55</t>
+          <t>2026-09-21 19:13</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>AMT</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>215.5</v>
+        <v>175.26</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
@@ -771,87 +771,87 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F7" s="4" t="b">
         <v>0</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>47.6</v>
+        <v>47.1</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4.09</v>
+        <v>0.39</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>225.8000030517578</v>
+        <v>180.9799957275391</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>186.0249938964844</v>
+        <v>160.0599975585938</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>226.93</v>
+        <v>181.88</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>186.02</v>
+        <v>160.06</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:55</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>559.8</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NEUTRAL_ZONE</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>47</v>
-      </c>
-      <c r="F8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>83</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="I8" t="n">
-        <v>584.72998046875</v>
-      </c>
-      <c r="J8" t="n">
-        <v>424.0315856933594</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21 19:14</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>369.58</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>NEAR_RESISTANCE (SHORT WATCH)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="F8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>385.5698852539062</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>331.4400024414062</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>387.5</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>331.44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20 10:55</t>
+          <t>2026-09-21 19:13</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>367.61</v>
+        <v>352.15</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
@@ -859,43 +859,43 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="F9" s="4" t="b">
         <v>0</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>29.2</v>
+        <v>59.8</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.01</v>
+        <v>0.64</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>385.5698852539062</v>
+        <v>366.5</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>330.0700073242188</v>
+        <v>325.010009765625</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>387.5</v>
+        <v>368.33</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>330.07</v>
+        <v>325.01</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-20 10:55</t>
+          <t>2026-09-21 19:13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>143.48</v>
+        <v>249.73</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -903,22 +903,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>41</v>
+        <v>55.7</v>
       </c>
       <c r="H10" t="n">
-        <v>2.01</v>
+        <v>0.48</v>
       </c>
       <c r="I10" t="n">
-        <v>149.5200042724609</v>
+        <v>250.3200073242188</v>
       </c>
       <c r="J10" t="n">
-        <v>102.3649978637695</v>
+        <v>168.4024963378906</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -928,62 +928,62 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:55</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>KO</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>88.15000000000001</v>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>NEAR_RESISTANCE (SHORT WATCH)</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="F11" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>92.48999786376953</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>79.97000122070312</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>92.95</v>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v>79.97</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-21 19:14</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>194.24</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NEUTRAL_ZONE</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>34</v>
+      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>56</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I11" t="n">
+        <v>208.8600006103516</v>
+      </c>
+      <c r="J11" t="n">
+        <v>142.8899993896484</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-20 10:55</t>
+          <t>2026-09-21 19:13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>197.29</v>
+        <v>259.48</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -991,22 +991,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>62.3</v>
+        <v>82.2</v>
       </c>
       <c r="H12" t="n">
-        <v>2.45</v>
+        <v>0.62</v>
       </c>
       <c r="I12" t="n">
-        <v>199.7599945068359</v>
+        <v>300</v>
       </c>
       <c r="J12" t="n">
-        <v>122.1500015258789</v>
+        <v>162.8999938964844</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1016,62 +1016,62 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:55</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ILMN</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>239.56</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NEUTRAL_ZONE</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>44</v>
-      </c>
-      <c r="F13" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="I13" t="n">
-        <v>249.1999969482422</v>
-      </c>
-      <c r="J13" t="n">
-        <v>173.2350006103516</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21 19:13</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>ICE</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>155.76</v>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>NEAR_RESISTANCE (SHORT WATCH)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="F13" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>164.6600036621094</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>121.7900009155273</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>165.48</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>121.79</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-20 10:55</t>
+          <t>2026-09-21 19:14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>424.36</v>
+        <v>205.82</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1079,22 +1079,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>73.5</v>
+        <v>70.3</v>
       </c>
       <c r="H14" t="n">
-        <v>1.99</v>
+        <v>0.42</v>
       </c>
       <c r="I14" t="n">
-        <v>428</v>
+        <v>206.1900024414062</v>
       </c>
       <c r="J14" t="n">
-        <v>244.6049957275391</v>
+        <v>125.2300033569336</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1106,16 +1106,16 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20 10:55</t>
+          <t>2026-09-21 19:13</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>AMT</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>173.99</v>
+        <v>88.01000000000001</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
@@ -1123,72 +1123,72 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F15" s="4" t="b">
         <v>0</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>38.1</v>
+        <v>47.6</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.19</v>
+        <v>0.64</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>180.9799957275391</v>
+        <v>92.48999786376953</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>160.0599975585938</v>
+        <v>80.69499969482422</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>181.88</v>
+        <v>92.95</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>160.06</v>
+        <v>80.69</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-20 10:55</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>NXPI</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>228.32</v>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>NEAR_SUPPORT (LONG WATCH)</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="F16" s="3" t="b">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-21 19:14</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>WBD</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>30.82</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NEUTRAL_ZONE</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>32</v>
+      </c>
+      <c r="F16" t="b">
         <v>1</v>
       </c>
-      <c r="G16" s="3" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>307.3800048828125</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>216.6600036621094</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>215.58</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>307.38</v>
+      <c r="G16" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I16" t="n">
+        <v>30.92000007629395</v>
+      </c>
+      <c r="J16" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Top_15_Triple_S_Watchlist.xlsx
+++ b/Top_15_Triple_S_Watchlist.xlsx
@@ -48,14 +48,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-        <bgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -534,16 +534,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-21 19:13</t>
+          <t>2026-09-22 18:09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>HSCS</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>744.5599999999999</v>
+        <v>4.68</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>81</v>
+        <v>40.6</v>
       </c>
       <c r="H2" t="n">
-        <v>1.02</v>
+        <v>2.92</v>
       </c>
       <c r="I2" t="n">
-        <v>749.489990234375</v>
+        <v>5.25</v>
       </c>
       <c r="J2" t="n">
-        <v>524.5189819335938</v>
+        <v>1.850000023841858</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -578,16 +578,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-21 19:13</t>
+          <t>2026-09-22 18:08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>GEMG</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>121.33</v>
+        <v>12</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -595,22 +595,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>75.3</v>
+        <v>69.2</v>
       </c>
       <c r="H3" t="n">
-        <v>0.44</v>
+        <v>3.86</v>
       </c>
       <c r="I3" t="n">
-        <v>142.3399963378906</v>
+        <v>13.5</v>
       </c>
       <c r="J3" t="n">
-        <v>81.79000091552734</v>
+        <v>4.849999904632568</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -622,16 +622,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-21 19:13</t>
+          <t>2026-09-22 18:06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>COSM</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>612.4</v>
+        <v>0.36</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -639,22 +639,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>85.7</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>0.53</v>
+        <v>1.97</v>
       </c>
       <c r="I4" t="n">
-        <v>615.989990234375</v>
+        <v>0.3758000135421753</v>
       </c>
       <c r="J4" t="n">
-        <v>424.0315856933594</v>
+        <v>0.1620000004768372</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -666,236 +666,236 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21 19:13</t>
+          <t>2026-09-22 18:09</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>HBANL</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>110.83</v>
+        <v>25.15</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>NEAR_SUPPORT (LONG WATCH)</t>
+          <t>NEAR_RESISTANCE (SHORT WATCH)</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="F5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>25.45000076293945</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>24.64979934692383</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>24.65</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 18:13</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>OXLCZ</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>NEAR_RESISTANCE (SHORT WATCH)</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="F6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>25.14999961853027</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>24.56999969482422</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>25.28</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>24.57</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-22 18:13</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ORBS</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NEUTRAL_ZONE</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>62</v>
+      </c>
+      <c r="F7" t="b">
         <v>1</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>124.7102966308594</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>107.3899993896484</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>106.85</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>124.71</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-21 19:14</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>ROKU</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>154.34</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>NEAR_RESISTANCE (SHORT WATCH)</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="F6" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>159.8899993896484</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>134.3600006103516</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>160.69</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>134.36</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-21 19:13</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>AMT</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>175.26</v>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>NEAR_RESISTANCE (SHORT WATCH)</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="F7" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>180.9799957275391</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>160.0599975585938</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>181.88</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>160.06</v>
+      <c r="G7" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.259999990463257</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5655999779701233</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-21 19:14</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>369.58</v>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>NEAR_RESISTANCE (SHORT WATCH)</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="F8" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>385.5698852539062</v>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>331.4400024414062</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>387.5</v>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>331.44</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-22 18:17</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TXXD</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>53.54</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NEUTRAL_ZONE</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>61</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I8" t="n">
+        <v>54.95989990234375</v>
+      </c>
+      <c r="J8" t="n">
+        <v>28.00100135803223</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-21 19:13</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>JPM</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>352.15</v>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>NEAR_RESISTANCE (SHORT WATCH)</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="F9" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>366.5</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>325.010009765625</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>368.33</v>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>325.01</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-22 18:03</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AIXI</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NEUTRAL_ZONE</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>60</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="I9" t="n">
+        <v>16.44999885559082</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.779999971389771</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-21 19:13</t>
+          <t>2026-09-22 18:08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>GENVR</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>249.73</v>
+        <v>2.55</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -903,22 +903,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="F10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>55.7</v>
+        <v>13.9</v>
       </c>
       <c r="H10" t="n">
-        <v>0.48</v>
+        <v>2.53</v>
       </c>
       <c r="I10" t="n">
-        <v>250.3200073242188</v>
+        <v>6.400000095367432</v>
       </c>
       <c r="J10" t="n">
-        <v>168.4024963378906</v>
+        <v>1.039999961853027</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -930,16 +930,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-21 19:14</t>
+          <t>2026-09-22 18:09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>HUBC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>194.24</v>
+        <v>4.57</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -947,22 +947,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="F11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>56</v>
+        <v>47.9</v>
       </c>
       <c r="H11" t="n">
-        <v>0.75</v>
+        <v>2.37</v>
       </c>
       <c r="I11" t="n">
-        <v>208.8600006103516</v>
+        <v>43.5</v>
       </c>
       <c r="J11" t="n">
-        <v>142.8899993896484</v>
+        <v>3.75</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -974,16 +974,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-21 19:13</t>
+          <t>2026-09-22 18:15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>SEAT</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>259.48</v>
+        <v>3.8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -991,22 +991,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="F12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>82.2</v>
+        <v>38.9</v>
       </c>
       <c r="H12" t="n">
-        <v>0.62</v>
+        <v>2.89</v>
       </c>
       <c r="I12" t="n">
-        <v>300</v>
+        <v>9.590000152587891</v>
       </c>
       <c r="J12" t="n">
-        <v>162.8999938964844</v>
+        <v>3.779999971389771</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1016,62 +1016,62 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-21 19:13</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>ICE</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>155.76</v>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>NEAR_RESISTANCE (SHORT WATCH)</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="F13" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>83.59999999999999</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>164.6600036621094</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>121.7900009155273</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>165.48</v>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v>121.79</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-22 18:03</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AEI</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NEUTRAL_ZONE</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>60</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.839900016784668</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.8149999976158142</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-21 19:14</t>
+          <t>2026-09-22 18:09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>HWH</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>205.82</v>
+        <v>2.68</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1079,22 +1079,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>70.3</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>0.42</v>
+        <v>1.51</v>
       </c>
       <c r="I14" t="n">
-        <v>206.1900024414062</v>
+        <v>2.785000085830688</v>
       </c>
       <c r="J14" t="n">
-        <v>125.2300033569336</v>
+        <v>1.129999995231628</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1104,91 +1104,91 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-21 19:13</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>KO</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>88.01000000000001</v>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 18:04</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>BDVL</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>26.51</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>NEAR_RESISTANCE (SHORT WATCH)</t>
         </is>
       </c>
-      <c r="E15" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="F15" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>92.48999786376953</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>80.69499969482422</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>92.95</v>
-      </c>
-      <c r="L15" s="4" t="n">
-        <v>80.69</v>
+      <c r="E15" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="F15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>27.02000045776367</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>25.69009971618652</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>27.16</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>25.69</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-09-21 19:14</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>WBD</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>30.82</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NEUTRAL_ZONE</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>32</v>
-      </c>
-      <c r="F16" t="b">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22 18:18</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>WTFCN</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>26.15</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>NEAR_SUPPORT (LONG WATCH)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="F16" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="G16" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I16" t="n">
-        <v>30.92000007629395</v>
-      </c>
-      <c r="J16" t="n">
-        <v>25.25</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
+      <c r="G16" s="4" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>26.46999931335449</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>25.85000038146973</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>25.72</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>26.47</v>
       </c>
     </row>
   </sheetData>

--- a/Top_15_Triple_S_Watchlist.xlsx
+++ b/Top_15_Triple_S_Watchlist.xlsx
@@ -33,7 +33,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -50,12 +50,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
         <bgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -86,7 +80,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -539,11 +532,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HSCS</t>
+          <t>GEMG</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4.68</v>
+        <v>12</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -557,16 +550,16 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>40.6</v>
+        <v>69.2</v>
       </c>
       <c r="H2" t="n">
-        <v>2.92</v>
+        <v>3.85</v>
       </c>
       <c r="I2" t="n">
-        <v>5.25</v>
+        <v>13.5</v>
       </c>
       <c r="J2" t="n">
-        <v>1.850000023841858</v>
+        <v>4.849999904632568</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -578,16 +571,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-22 18:08</t>
+          <t>2026-09-22 18:10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GEMG</t>
+          <t>HSCS</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>4.68</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -601,16 +594,16 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>69.2</v>
+        <v>40.6</v>
       </c>
       <c r="H3" t="n">
-        <v>3.86</v>
+        <v>2.92</v>
       </c>
       <c r="I3" t="n">
-        <v>13.5</v>
+        <v>5.25</v>
       </c>
       <c r="J3" t="n">
-        <v>4.849999904632568</v>
+        <v>1.850000023841858</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -620,97 +613,97 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 18:10</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>HBANL</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>NEAR_RESISTANCE (SHORT WATCH)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="F4" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>25.45000076293945</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>24.64979934692383</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>24.65</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026-09-22 18:06</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>COSM</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C5" t="n">
         <v>0.36</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>NEUTRAL_ZONE</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E5" t="n">
         <v>64</v>
       </c>
-      <c r="F4" t="b">
+      <c r="F5" t="b">
         <v>1</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G5" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H5" t="n">
         <v>1.97</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I5" t="n">
         <v>0.3758000135421753</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J5" t="n">
         <v>0.1620000004768372</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22 18:09</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>HBANL</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>25.15</v>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>NEAR_RESISTANCE (SHORT WATCH)</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="F5" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>25.45000076293945</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>24.64979934692383</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>25.58</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>24.65</v>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 18:13</t>
+          <t>2026-09-22 18:14</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -754,7 +747,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-22 18:13</t>
+          <t>2026-09-22 18:14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -763,7 +756,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -771,16 +764,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>71.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="I7" t="n">
         <v>1.259999990463257</v>
@@ -798,7 +791,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-22 18:17</t>
+          <t>2026-09-22 18:19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -842,16 +835,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-22 18:03</t>
+          <t>2026-09-22 18:09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AIXI</t>
+          <t>GENVR</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.87</v>
+        <v>2.55</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -865,16 +858,16 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>30.7</v>
+        <v>13.9</v>
       </c>
       <c r="H9" t="n">
-        <v>2.77</v>
+        <v>3.41</v>
       </c>
       <c r="I9" t="n">
-        <v>16.44999885559082</v>
+        <v>6.400000095367432</v>
       </c>
       <c r="J9" t="n">
-        <v>1.779999971389771</v>
+        <v>1.039999961853027</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -886,16 +879,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-22 18:08</t>
+          <t>2026-09-22 18:10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GENVR</t>
+          <t>HUBC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.55</v>
+        <v>4.53</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -909,16 +902,16 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>13.9</v>
+        <v>47.5</v>
       </c>
       <c r="H10" t="n">
-        <v>2.53</v>
+        <v>2.37</v>
       </c>
       <c r="I10" t="n">
-        <v>6.400000095367432</v>
+        <v>43.5</v>
       </c>
       <c r="J10" t="n">
-        <v>1.039999961853027</v>
+        <v>3.75</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -930,16 +923,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-22 18:09</t>
+          <t>2026-09-22 18:17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HUBC</t>
+          <t>SEAT</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4.57</v>
+        <v>3.8</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -953,16 +946,16 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>47.9</v>
+        <v>38.9</v>
       </c>
       <c r="H11" t="n">
-        <v>2.37</v>
+        <v>2.89</v>
       </c>
       <c r="I11" t="n">
-        <v>43.5</v>
+        <v>9.590000152587891</v>
       </c>
       <c r="J11" t="n">
-        <v>3.75</v>
+        <v>3.779999971389771</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -974,16 +967,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-22 18:15</t>
+          <t>2026-09-22 18:03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SEAT</t>
+          <t>AIXI</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3.8</v>
+        <v>1.87</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -997,16 +990,16 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>38.9</v>
+        <v>30.7</v>
       </c>
       <c r="H12" t="n">
-        <v>2.89</v>
+        <v>2.77</v>
       </c>
       <c r="I12" t="n">
-        <v>9.590000152587891</v>
+        <v>16.44999885559082</v>
       </c>
       <c r="J12" t="n">
-        <v>3.779999971389771</v>
+        <v>1.779999971389771</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1062,7 +1055,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-22 18:09</t>
+          <t>2026-09-22 18:10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1148,47 +1141,47 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-22 18:18</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>WTFCN</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>26.15</v>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>NEAR_SUPPORT (LONG WATCH)</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="n">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 18:11</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>IUS</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>69.03</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>NEAR_RESISTANCE (SHORT WATCH)</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="F16" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>53.4</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>26.46999931335449</v>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>25.85000038146973</v>
-      </c>
-      <c r="K16" s="4" t="n">
-        <v>25.72</v>
-      </c>
-      <c r="L16" s="4" t="n">
-        <v>26.47</v>
+      <c r="F16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>70.64499664306641</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>65.38009643554688</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>65.38</v>
       </c>
     </row>
   </sheetData>
